--- a/input/ut_input.xlsx
+++ b/input/ut_input.xlsx
@@ -16,7 +16,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="35" uniqueCount="26">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="40" uniqueCount="30">
   <si>
     <t>TC001</t>
   </si>
@@ -94,6 +94,18 @@
   </si>
   <si>
     <t>special_character_validation</t>
+  </si>
+  <si>
+    <t>TC011</t>
+  </si>
+  <si>
+    <t>row_count</t>
+  </si>
+  <si>
+    <t>bronze_customers_delta</t>
+  </si>
+  <si>
+    <t>silver_customers_delta</t>
   </si>
 </sst>
 </file>
@@ -428,7 +440,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:G11"/>
+  <dimension ref="A1:G12"/>
   <sheetFormatPr defaultRowHeight="14.5"/>
   <cols>
     <col min="1" max="1" width="16.81640625" customWidth="1"/>
@@ -566,6 +578,23 @@
         <v>24</v>
       </c>
       <c r="E11" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="12" spans="1:7">
+      <c r="A12" t="s">
+        <v>26</v>
+      </c>
+      <c r="B12" t="s">
+        <v>27</v>
+      </c>
+      <c r="C12" t="s">
+        <v>28</v>
+      </c>
+      <c r="D12" t="s">
+        <v>29</v>
+      </c>
+      <c r="E12" t="s">
         <v>11</v>
       </c>
     </row>
